--- a/#Bitcoin_anonymized.xlsx
+++ b/#Bitcoin_anonymized.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14900,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25073,7 +25073,7 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25115,7 +25115,7 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25157,7 +25157,7 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25202,7 +25202,7 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25248,7 +25248,7 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25290,7 +25290,7 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25420,7 +25420,7 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25464,7 +25464,7 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25506,7 +25506,7 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30002,7 +30002,7 @@
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="J857" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="J858" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30122,7 +30122,7 @@
       </c>
       <c r="J859" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30164,7 +30164,7 @@
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
